--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer C1</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd7a10fab4aead6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Feature Engineer</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,38 +657,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8442abf91777c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Fresh Food QA Technician</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Full Stack Java Technical Specialist - React.js</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresh Food QA Technician</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Fullstack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af690b2327755c54</t>
+          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jr. Feature Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3a9fd6adbb852f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vasa Fitness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+          <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Fullstack Developer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1020,531 +1020,6 @@
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=461471cb36992ab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Associate</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, PySpark, Kafka, Snowflake, ETL, Splunk</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54b42443ee3c4437</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IT Data Solutions Developer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Atrium Health</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5097ade3e79b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Vasa Fitness</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Kearney, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Grand Island, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Hybrid</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c67eab5c67331a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Attain Finance</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Databricks Engineer</t>
+          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f289865d551fa1a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4944b59a58404b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Java Technical Specialist - React.js</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
+          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Snowflake Engineer</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fresh Food QA Technician</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,322 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Full Stack Java Technical Specialist - React.js</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fabric Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sr Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e08b28ff2bdfcb80</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vasa Fitness</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3a253ea4b50de</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Specialist - Data Engineering</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Attain Finance</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WFP Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644f70485107abbe</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
+          <t>Full Stack Developer React/ Java/ Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, PySpark, Scala, PostgreSQL, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Full Stack Java Technical Specialist - React.js</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,110 +601,75 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
+          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Java Technical Specialist - React.js</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Specialist - Data Engineering</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
         </is>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fabric Platform Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,25 +618,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Aldie, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
+          <t>https://www.indeed.com/viewjob?jk=0215398446cd7f0b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer React/ Java/ Python</t>
+          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29d621da3e9a4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
         </is>
       </c>
     </row>
@@ -608,68 +608,103 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>GCP Application Technical Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b49ae82a293e4f9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Sr Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Specialist - Data Engineering</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>LTIMindtree</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
         </is>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
+          <t>https://www.indeed.com/viewjob?jk=87befe694c7b985a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
+          <t>https://www.indeed.com/viewjob?jk=be71c50bf15a0668</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Java Technical Specialist - React.js</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,112 +601,1827 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3437af494333f678</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Application Technical Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b49ae82a293e4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=54cb5839d7f1ff18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a852273f7c50ace</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camden Property Trust</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, HBase, Spark, Scala, Kafka, Oracle, MySQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b23c16e9f7fa792e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, HBase, Spark, Scala, Kafka, Oracle, MySQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac9dc3219cfc4a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2266c4dba2263dcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, HBase, Spark, PySpark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c005a7e163f3e45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2138ac157376b704</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, MySQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=330a92d6908ce8a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Hadoop, HDFS, Scala, MySQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=957be306b670cbe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113b681733f9747f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, HBase, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=258440f6c426d01d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ingram Micro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a30d714c22c8735</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=668fd578e5ad205b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, MLOps</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eaf063221a10b37</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ce59f430b705383</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Full Stack Java Technical Specialist - React.js</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GCP Application Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>IAM, GCP, BigQuery, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b49ae82a293e4f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1479a392d9628a14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr Security Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Specialist - Data Engineering</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>LTIMindtree</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D50" t="n">
         <v>10.4</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50166ea86bb9965</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786d28f512935cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, MySQL, NoSQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b71213ece018bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, ETL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e43322fd80b5294</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, ETL, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edf61855d4ab5e16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32f351a5adb8088f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, MySQL, Cassandra, NoSQL, Data Modeling, Tableau, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b38ea20568618d5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-21.xlsx
+++ b/results/job_matches_2026-06-21.xlsx
@@ -1063,7 +1063,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0cbcd1f68bbd17</t>
+          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad2dad57da48016</t>
+          <t>https://www.indeed.com/viewjob?jk=8c56d229b10aedad</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Java Technical Specialist - React.js</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, Splunk, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
+          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe0d6afd5890323</t>
+          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce50156e09e284be</t>
+          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6205d2f26b1a8bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da39ecae1ec3ea0f</t>
+          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,15 +1493,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ae1753ad2a27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a792ded5789cd</t>
+          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53032a4f73d83e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4919174f0cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562e8a2839504d14</t>
+          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64bab937e1605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Application Technical Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Kafka, MySQL</t>
+          <t>IAM, GCP, BigQuery, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8efbd88a354542d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b49ae82a293e4f9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Application Technical Specialist</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b49ae82a293e4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Kafka, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e185b13ff1bfe4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. BI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b570e647466948e</t>
+          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, ETL, Tableau</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83344ad97f6d0723</t>
+          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,24 +1921,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed47cf62aeed008b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6f5314015483d</t>
+          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975ac3cab8fe8b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Spark, PySpark, Scala, ETL, Tableau, Python</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684ac425090f80d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Oracle, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f36b69a2642649b</t>
+          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MySQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576587c3beb8fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Scala, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8e2f411bfd2f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb58a77c3b1339a</t>
         </is>
       </c>
     </row>
